--- a/iFST_local_PsychoPy/messages.xlsx
+++ b/iFST_local_PsychoPy/messages.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_PsychoPy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A7ACB62-C721-4533-A069-09ADE2C17C78}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="8_{439F560A-EC9A-4A85-BCCA-B610A865D2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E455B5-61F5-4C8F-82BC-31FC449F642E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="223">
   <si>
     <t>EN</t>
   </si>
@@ -843,9 +843,6 @@
   </si>
   <si>
     <t>right_msg</t>
-  </si>
-  <si>
-    <t>Rechte</t>
   </si>
 </sst>
 </file>
@@ -949,6 +946,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2050,7 +2051,7 @@
         <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>223</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -2083,6 +2084,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -2196,33 +2212,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2243,9 +2236,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>